--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852388</v>
+        <v>122852490</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584009</v>
+        <v>583911</v>
       </c>
       <c r="R2" t="n">
-        <v>6321450</v>
+        <v>6321488</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122844758</v>
+        <v>122843814</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +808,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583960</v>
+        <v>584059</v>
       </c>
       <c r="R3" t="n">
-        <v>6321445</v>
+        <v>6321402</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122843814</v>
+        <v>122852388</v>
       </c>
       <c r="B4" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,50 +919,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584059</v>
+        <v>584009</v>
       </c>
       <c r="R4" t="n">
-        <v>6321402</v>
+        <v>6321450</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,39 +988,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122843791</v>
+        <v>122844784</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,40 +1040,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1063,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584084</v>
+        <v>583938</v>
       </c>
       <c r="R5" t="n">
-        <v>6321402</v>
+        <v>6321489</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,22 +1122,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122852381</v>
+        <v>122844882</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1146,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,23 +1172,19 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584037</v>
+        <v>583906</v>
       </c>
       <c r="R6" t="n">
-        <v>6321415</v>
+        <v>6321498</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,50 +1211,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122845389</v>
+        <v>122844758</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,24 +1273,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583986</v>
+        <v>583960</v>
       </c>
       <c r="R7" t="n">
-        <v>6321434</v>
+        <v>6321445</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,11 +1316,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122844882</v>
+        <v>122843791</v>
       </c>
       <c r="B8" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,30 +1354,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1401,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583906</v>
+        <v>584084</v>
       </c>
       <c r="R8" t="n">
-        <v>6321498</v>
+        <v>6321402</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,22 +1446,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122844784</v>
+        <v>122845389</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,30 +1470,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1507,13 +1502,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583938</v>
+        <v>583986</v>
       </c>
       <c r="R9" t="n">
-        <v>6321489</v>
+        <v>6321434</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,6 +1538,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122852490</v>
+        <v>122852381</v>
       </c>
       <c r="B10" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,30 +1581,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583911</v>
+        <v>584037</v>
       </c>
       <c r="R10" t="n">
-        <v>6321488</v>
+        <v>6321415</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1687,6 +1687,1007 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122872727</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>583975</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6321433</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122872699</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105461</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>583992</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6321455</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122872737</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>583966</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6321457</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122872705</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>583990</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6321458</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122872764</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95126</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583884</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6321510</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122872722</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>583996</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6321453</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122872713</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583965</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6321466</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122872697</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>583992</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6321455</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122872731</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vidflagen, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>583975</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6321433</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852490</v>
+        <v>122843791</v>
       </c>
       <c r="B2" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583911</v>
+        <v>584084</v>
       </c>
       <c r="R2" t="n">
-        <v>6321488</v>
+        <v>6321402</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,47 +762,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122843814</v>
+        <v>122844882</v>
       </c>
       <c r="B3" t="n">
         <v>105461</v>
@@ -831,12 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584059</v>
+        <v>583906</v>
       </c>
       <c r="R3" t="n">
-        <v>6321402</v>
+        <v>6321498</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,19 +885,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122852388</v>
+        <v>122852381</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -942,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -955,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584009</v>
+        <v>584037</v>
       </c>
       <c r="R4" t="n">
-        <v>6321450</v>
+        <v>6321415</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1028,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122844784</v>
+        <v>122852490</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>105461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,42 +1030,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583938</v>
+        <v>583911</v>
       </c>
       <c r="R5" t="n">
-        <v>6321489</v>
+        <v>6321488</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,36 +1099,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122844882</v>
+        <v>122843814</v>
       </c>
       <c r="B6" t="n">
         <v>105461</v>
@@ -1169,7 +1174,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1178,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583906</v>
+        <v>584059</v>
       </c>
       <c r="R6" t="n">
-        <v>6321498</v>
+        <v>6321402</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,19 +1238,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122844758</v>
+        <v>122845389</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1273,20 +1283,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583960</v>
+        <v>583986</v>
       </c>
       <c r="R7" t="n">
-        <v>6321445</v>
+        <v>6321434</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,6 +1330,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122843791</v>
+        <v>122844758</v>
       </c>
       <c r="B8" t="n">
         <v>98355</v>
@@ -1375,34 +1394,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584084</v>
+        <v>583960</v>
       </c>
       <c r="R8" t="n">
-        <v>6321402</v>
+        <v>6321445</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,22 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122845389</v>
+        <v>122844784</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,30 +1475,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1502,13 +1507,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583986</v>
+        <v>583938</v>
       </c>
       <c r="R9" t="n">
-        <v>6321434</v>
+        <v>6321489</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,11 +1543,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122852381</v>
+        <v>122852388</v>
       </c>
       <c r="B10" t="n">
         <v>98355</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584037</v>
+        <v>584009</v>
       </c>
       <c r="R10" t="n">
-        <v>6321415</v>
+        <v>6321450</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872727</v>
+        <v>122872737</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,35 +1702,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1738,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583975</v>
+        <v>583966</v>
       </c>
       <c r="R11" t="n">
-        <v>6321433</v>
+        <v>6321457</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1786,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1801,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122872699</v>
+        <v>122872722</v>
       </c>
       <c r="B12" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,30 +1816,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1849,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583992</v>
+        <v>583996</v>
       </c>
       <c r="R12" t="n">
-        <v>6321455</v>
+        <v>6321453</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1912,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122872737</v>
+        <v>122872705</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,39 +1927,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1964,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583966</v>
+        <v>583990</v>
       </c>
       <c r="R13" t="n">
-        <v>6321457</v>
+        <v>6321458</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2008,6 +2007,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872705</v>
+        <v>122872731</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2038,25 +2038,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2064,9 +2064,13 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583990</v>
+        <v>583975</v>
       </c>
       <c r="R14" t="n">
-        <v>6321458</v>
+        <v>6321433</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2118,7 +2122,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2137,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872764</v>
+        <v>122872699</v>
       </c>
       <c r="B15" t="n">
-        <v>95126</v>
+        <v>105461</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,24 +2156,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2181,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583884</v>
+        <v>583992</v>
       </c>
       <c r="R15" t="n">
-        <v>6321510</v>
+        <v>6321455</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2251,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872722</v>
+        <v>122872727</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2279,7 +2286,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2292,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583996</v>
+        <v>583975</v>
       </c>
       <c r="R16" t="n">
-        <v>6321453</v>
+        <v>6321433</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2355,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872713</v>
+        <v>122872697</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2390,7 +2397,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2403,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583965</v>
+        <v>583992</v>
       </c>
       <c r="R17" t="n">
-        <v>6321466</v>
+        <v>6321455</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2466,7 +2473,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122872697</v>
+        <v>122872713</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2501,7 +2508,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2514,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583992</v>
+        <v>583965</v>
       </c>
       <c r="R18" t="n">
-        <v>6321455</v>
+        <v>6321466</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2577,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122872731</v>
+        <v>122872764</v>
       </c>
       <c r="B19" t="n">
-        <v>57848</v>
+        <v>95126</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2593,35 +2600,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2629,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583975</v>
+        <v>583884</v>
       </c>
       <c r="R19" t="n">
-        <v>6321433</v>
+        <v>6321510</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2673,6 +2672,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2688,6 +2688,1152 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122873574</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>583893</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6321535</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122873660</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>583872</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6321489</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122873541</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>583972</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6321426</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122873603</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91354</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>583857</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6321560</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122873533</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>584050</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6321450</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122873525</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>584055</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6321441</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122873552</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>583961</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6321560</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122873510</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>584086</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6321399</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122873563</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>583933</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6321513</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122873636</v>
+      </c>
+      <c r="B29" t="n">
+        <v>95128</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Älgerum 5:9, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>583840</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6321548</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122843791</v>
+        <v>122843814</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,18 +718,13 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584084</v>
+        <v>584059</v>
       </c>
       <c r="R2" t="n">
         <v>6321402</v>
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122844882</v>
+        <v>122852388</v>
       </c>
       <c r="B3" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,45 +798,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583906</v>
+        <v>584009</v>
       </c>
       <c r="R3" t="n">
-        <v>6321498</v>
+        <v>6321450</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,39 +867,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122852381</v>
+        <v>122844784</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,46 +919,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584037</v>
+        <v>583938</v>
       </c>
       <c r="R4" t="n">
-        <v>6321415</v>
+        <v>6321489</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,50 +984,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122852490</v>
+        <v>122845389</v>
       </c>
       <c r="B5" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,49 +1025,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583911</v>
+        <v>583986</v>
       </c>
       <c r="R5" t="n">
-        <v>6321488</v>
+        <v>6321434</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,19 +1090,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,29 +1106,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122843814</v>
+        <v>122852490</v>
       </c>
       <c r="B6" t="n">
-        <v>105461</v>
+        <v>105463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,27 +1159,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584059</v>
+        <v>583911</v>
       </c>
       <c r="R6" t="n">
-        <v>6321402</v>
+        <v>6321488</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,39 +1205,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122845389</v>
+        <v>122852381</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,22 +1280,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583986</v>
+        <v>584037</v>
       </c>
       <c r="R7" t="n">
-        <v>6321434</v>
+        <v>6321415</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,14 +1326,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,28 +1347,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122844758</v>
+        <v>122843791</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,20 +1399,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583960</v>
+        <v>584084</v>
       </c>
       <c r="R8" t="n">
-        <v>6321445</v>
+        <v>6321402</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122844784</v>
+        <v>122844758</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,45 +1494,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583938</v>
+        <v>583960</v>
       </c>
       <c r="R9" t="n">
-        <v>6321489</v>
+        <v>6321445</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122852388</v>
+        <v>122844882</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,49 +1596,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584009</v>
+        <v>583906</v>
       </c>
       <c r="R10" t="n">
-        <v>6321450</v>
+        <v>6321498</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,50 +1661,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872737</v>
+        <v>122872705</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,39 +1702,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1742,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583966</v>
+        <v>583990</v>
       </c>
       <c r="R11" t="n">
-        <v>6321457</v>
+        <v>6321458</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,6 +1782,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1804,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122872722</v>
+        <v>122872764</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>95128</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,32 +1813,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1852,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583996</v>
+        <v>583884</v>
       </c>
       <c r="R12" t="n">
-        <v>6321453</v>
+        <v>6321510</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122872705</v>
+        <v>122872737</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,35 +1920,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583990</v>
+        <v>583966</v>
       </c>
       <c r="R13" t="n">
-        <v>6321458</v>
+        <v>6321457</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +2004,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2026,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872731</v>
+        <v>122872699</v>
       </c>
       <c r="B14" t="n">
-        <v>57848</v>
+        <v>105463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,35 +2038,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583975</v>
+        <v>583992</v>
       </c>
       <c r="R14" t="n">
-        <v>6321433</v>
+        <v>6321455</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2122,6 +2114,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2140,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872699</v>
+        <v>122872722</v>
       </c>
       <c r="B15" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,30 +2145,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2188,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583992</v>
+        <v>583996</v>
       </c>
       <c r="R15" t="n">
-        <v>6321455</v>
+        <v>6321453</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2251,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872727</v>
+        <v>122872731</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,35 +2256,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2343,7 +2340,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2365,7 +2361,7 @@
         <v>122872697</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,7 +2472,7 @@
         <v>122872713</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2584,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122872764</v>
+        <v>122872727</v>
       </c>
       <c r="B19" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,28 +2592,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583884</v>
+        <v>583975</v>
       </c>
       <c r="R19" t="n">
-        <v>6321510</v>
+        <v>6321433</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873574</v>
+        <v>122873533</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,35 +2703,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2739,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583893</v>
+        <v>584050</v>
       </c>
       <c r="R20" t="n">
-        <v>6321535</v>
+        <v>6321450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,6 +2791,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2801,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873660</v>
+        <v>122873636</v>
       </c>
       <c r="B21" t="n">
-        <v>105463</v>
+        <v>95128</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2817,34 +2826,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2853,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583872</v>
+        <v>583840</v>
       </c>
       <c r="R21" t="n">
-        <v>6321489</v>
+        <v>6321548</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873541</v>
+        <v>122873660</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2928,37 +2933,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2972,10 +2973,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583972</v>
+        <v>583872</v>
       </c>
       <c r="R22" t="n">
-        <v>6321426</v>
+        <v>6321489</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3149,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873533</v>
+        <v>122873552</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,43 +3162,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3205,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584050</v>
+        <v>583961</v>
       </c>
       <c r="R24" t="n">
-        <v>6321450</v>
+        <v>6321560</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3249,7 +3242,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3268,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873525</v>
+        <v>122873510</v>
       </c>
       <c r="B25" t="n">
         <v>98357</v>
@@ -3303,7 +3295,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3324,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584055</v>
+        <v>584086</v>
       </c>
       <c r="R25" t="n">
-        <v>6321441</v>
+        <v>6321399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3387,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873552</v>
+        <v>122873525</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3399,35 +3391,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583961</v>
+        <v>584055</v>
       </c>
       <c r="R26" t="n">
-        <v>6321560</v>
+        <v>6321441</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3479,6 +3479,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3497,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122873510</v>
+        <v>122873574</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3509,43 +3510,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3553,10 +3546,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584086</v>
+        <v>583893</v>
       </c>
       <c r="R27" t="n">
-        <v>6321399</v>
+        <v>6321535</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3597,7 +3590,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3726,10 +3718,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122873636</v>
+        <v>122873541</v>
       </c>
       <c r="B29" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3738,34 +3730,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583840</v>
+        <v>583972</v>
       </c>
       <c r="R29" t="n">
-        <v>6321548</v>
+        <v>6321426</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122843814</v>
+        <v>122852381</v>
       </c>
       <c r="B2" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584059</v>
+        <v>584037</v>
       </c>
       <c r="R2" t="n">
-        <v>6321402</v>
+        <v>6321415</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,39 +756,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852388</v>
+        <v>122852490</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +808,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -834,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584009</v>
+        <v>583911</v>
       </c>
       <c r="R3" t="n">
-        <v>6321450</v>
+        <v>6321488</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -907,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122844784</v>
+        <v>122852388</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,42 +929,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583938</v>
+        <v>584009</v>
       </c>
       <c r="R4" t="n">
-        <v>6321489</v>
+        <v>6321450</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,29 +998,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1124,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122852490</v>
+        <v>122844758</v>
       </c>
       <c r="B6" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,49 +1161,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583911</v>
+        <v>583960</v>
       </c>
       <c r="R6" t="n">
-        <v>6321488</v>
+        <v>6321445</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,47 +1222,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122852381</v>
+        <v>122843791</v>
       </c>
       <c r="B7" t="n">
         <v>98357</v>
@@ -1280,26 +1286,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584037</v>
+        <v>584084</v>
       </c>
       <c r="R7" t="n">
-        <v>6321415</v>
+        <v>6321402</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,50 +1338,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122843791</v>
+        <v>122844784</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,40 +1379,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1420,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584084</v>
+        <v>583938</v>
       </c>
       <c r="R8" t="n">
-        <v>6321402</v>
+        <v>6321489</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122844758</v>
+        <v>122844882</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,38 +1485,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583960</v>
+        <v>583906</v>
       </c>
       <c r="R9" t="n">
-        <v>6321445</v>
+        <v>6321498</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1584,7 +1579,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122844882</v>
+        <v>122843814</v>
       </c>
       <c r="B10" t="n">
         <v>105463</v>
@@ -1619,7 +1614,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1628,13 +1628,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583906</v>
+        <v>584059</v>
       </c>
       <c r="R10" t="n">
-        <v>6321498</v>
+        <v>6321402</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,22 +1678,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872705</v>
+        <v>122872731</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1728,9 +1728,13 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1738,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583990</v>
+        <v>583975</v>
       </c>
       <c r="R11" t="n">
-        <v>6321458</v>
+        <v>6321433</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1786,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1908,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122872737</v>
+        <v>122872697</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,39 +1923,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1960,10 +1959,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583966</v>
+        <v>583992</v>
       </c>
       <c r="R13" t="n">
-        <v>6321457</v>
+        <v>6321455</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2004,6 +2003,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872699</v>
+        <v>122872727</v>
       </c>
       <c r="B14" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,30 +2034,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583992</v>
+        <v>583975</v>
       </c>
       <c r="R14" t="n">
-        <v>6321455</v>
+        <v>6321433</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872722</v>
+        <v>122872713</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583996</v>
+        <v>583965</v>
       </c>
       <c r="R15" t="n">
-        <v>6321453</v>
+        <v>6321466</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872731</v>
+        <v>122872699</v>
       </c>
       <c r="B16" t="n">
-        <v>57848</v>
+        <v>105463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,35 +2260,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2296,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583975</v>
+        <v>583992</v>
       </c>
       <c r="R16" t="n">
-        <v>6321433</v>
+        <v>6321455</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2340,6 +2336,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2358,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872697</v>
+        <v>122872722</v>
       </c>
       <c r="B17" t="n">
         <v>98357</v>
@@ -2393,7 +2390,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2406,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583992</v>
+        <v>583996</v>
       </c>
       <c r="R17" t="n">
-        <v>6321455</v>
+        <v>6321453</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2466,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122872713</v>
+        <v>122872705</v>
       </c>
       <c r="B18" t="n">
         <v>98357</v>
@@ -2504,7 +2501,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2517,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583965</v>
+        <v>583990</v>
       </c>
       <c r="R18" t="n">
-        <v>6321466</v>
+        <v>6321458</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2580,10 +2577,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122872727</v>
+        <v>122872737</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,35 +2589,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2628,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583975</v>
+        <v>583966</v>
       </c>
       <c r="R19" t="n">
-        <v>6321433</v>
+        <v>6321457</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2672,7 +2673,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873533</v>
+        <v>122873636</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,42 +2703,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2747,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584050</v>
+        <v>583840</v>
       </c>
       <c r="R20" t="n">
-        <v>6321450</v>
+        <v>6321548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2810,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873636</v>
+        <v>122873525</v>
       </c>
       <c r="B21" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2822,34 +2814,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583840</v>
+        <v>584055</v>
       </c>
       <c r="R21" t="n">
-        <v>6321548</v>
+        <v>6321441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873660</v>
+        <v>122873603</v>
       </c>
       <c r="B22" t="n">
-        <v>105463</v>
+        <v>91354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,35 +2937,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2973,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583872</v>
+        <v>583857</v>
       </c>
       <c r="R22" t="n">
-        <v>6321489</v>
+        <v>6321560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122873603</v>
+        <v>122873563</v>
       </c>
       <c r="B23" t="n">
-        <v>91354</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,38 +3047,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3087,10 +3083,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583857</v>
+        <v>583933</v>
       </c>
       <c r="R23" t="n">
-        <v>6321560</v>
+        <v>6321513</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3131,7 +3127,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3150,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873552</v>
+        <v>122873541</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,35 +3157,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3198,10 +3201,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583961</v>
+        <v>583972</v>
       </c>
       <c r="R24" t="n">
-        <v>6321560</v>
+        <v>6321426</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3242,6 +3245,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3260,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873510</v>
+        <v>122873552</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,43 +3276,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3316,10 +3312,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584086</v>
+        <v>583961</v>
       </c>
       <c r="R25" t="n">
-        <v>6321399</v>
+        <v>6321560</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3360,7 +3356,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3379,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873525</v>
+        <v>122873574</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,43 +3386,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3435,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584055</v>
+        <v>583893</v>
       </c>
       <c r="R26" t="n">
-        <v>6321441</v>
+        <v>6321535</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3479,7 +3466,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3498,10 +3484,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122873574</v>
+        <v>122873660</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>105463</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,35 +3496,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3546,10 +3536,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583893</v>
+        <v>583872</v>
       </c>
       <c r="R27" t="n">
-        <v>6321535</v>
+        <v>6321489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3590,6 +3580,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3608,10 +3599,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122873563</v>
+        <v>122873510</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3620,35 +3611,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3656,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583933</v>
+        <v>584086</v>
       </c>
       <c r="R28" t="n">
-        <v>6321513</v>
+        <v>6321399</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3700,6 +3699,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122873541</v>
+        <v>122873533</v>
       </c>
       <c r="B29" t="n">
         <v>98357</v>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583972</v>
+        <v>584050</v>
       </c>
       <c r="R29" t="n">
-        <v>6321426</v>
+        <v>6321450</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122844758</v>
+        <v>122843791</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1182,20 +1182,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583960</v>
+        <v>584084</v>
       </c>
       <c r="R6" t="n">
-        <v>6321445</v>
+        <v>6321402</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,19 +1253,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122843791</v>
+        <v>122844758</v>
       </c>
       <c r="B7" t="n">
         <v>98357</v>
@@ -1284,34 +1298,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584084</v>
+        <v>583960</v>
       </c>
       <c r="R7" t="n">
-        <v>6321402</v>
+        <v>6321445</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,12 +1355,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852381</v>
+        <v>122843791</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,26 +710,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584037</v>
+        <v>584084</v>
       </c>
       <c r="R2" t="n">
-        <v>6321415</v>
+        <v>6321402</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,50 +762,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852490</v>
+        <v>122845389</v>
       </c>
       <c r="B3" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,49 +803,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583911</v>
+        <v>583986</v>
       </c>
       <c r="R3" t="n">
-        <v>6321488</v>
+        <v>6321434</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,19 +868,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,29 +884,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122852388</v>
+        <v>122844784</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,46 +914,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584009</v>
+        <v>583938</v>
       </c>
       <c r="R4" t="n">
-        <v>6321450</v>
+        <v>6321489</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,50 +979,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122845389</v>
+        <v>122843814</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,30 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583986</v>
+        <v>584059</v>
       </c>
       <c r="R5" t="n">
-        <v>6321434</v>
+        <v>6321402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,11 +1095,6 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1137,22 +1107,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122843791</v>
+        <v>122844758</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,34 +1152,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584084</v>
+        <v>583960</v>
       </c>
       <c r="R6" t="n">
-        <v>6321402</v>
+        <v>6321445</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,22 +1209,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122844758</v>
+        <v>122844882</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,38 +1233,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583960</v>
+        <v>583906</v>
       </c>
       <c r="R7" t="n">
-        <v>6321445</v>
+        <v>6321498</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1367,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122844784</v>
+        <v>122852490</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,42 +1339,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583938</v>
+        <v>583911</v>
       </c>
       <c r="R8" t="n">
-        <v>6321489</v>
+        <v>6321488</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,39 +1408,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122844882</v>
+        <v>122852381</v>
       </c>
       <c r="B9" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1460,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1511,19 +1486,23 @@
           <t>30</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583906</v>
+        <v>584037</v>
       </c>
       <c r="R9" t="n">
-        <v>6321498</v>
+        <v>6321415</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,39 +1529,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122843814</v>
+        <v>122852388</v>
       </c>
       <c r="B10" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,50 +1581,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584059</v>
+        <v>584009</v>
       </c>
       <c r="R10" t="n">
-        <v>6321402</v>
+        <v>6321450</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,39 +1650,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872731</v>
+        <v>122872764</v>
       </c>
       <c r="B11" t="n">
-        <v>57848</v>
+        <v>95136</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,35 +1706,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1742,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583975</v>
+        <v>583884</v>
       </c>
       <c r="R11" t="n">
-        <v>6321433</v>
+        <v>6321510</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,6 +1778,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1804,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122872764</v>
+        <v>122872727</v>
       </c>
       <c r="B12" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,28 +1809,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1848,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583884</v>
+        <v>583975</v>
       </c>
       <c r="R12" t="n">
-        <v>6321510</v>
+        <v>6321433</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1911,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122872697</v>
+        <v>122872705</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,7 +1943,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1959,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583992</v>
+        <v>583990</v>
       </c>
       <c r="R13" t="n">
-        <v>6321455</v>
+        <v>6321458</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2022,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872727</v>
+        <v>122872699</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,30 +2031,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2070,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583975</v>
+        <v>583992</v>
       </c>
       <c r="R14" t="n">
-        <v>6321433</v>
+        <v>6321455</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872713</v>
+        <v>122872731</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,35 +2142,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2181,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583965</v>
+        <v>583975</v>
       </c>
       <c r="R15" t="n">
-        <v>6321466</v>
+        <v>6321433</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2226,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872699</v>
+        <v>122872713</v>
       </c>
       <c r="B16" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,30 +2256,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583992</v>
+        <v>583965</v>
       </c>
       <c r="R16" t="n">
-        <v>6321455</v>
+        <v>6321466</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872722</v>
+        <v>122872697</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583996</v>
+        <v>583992</v>
       </c>
       <c r="R17" t="n">
-        <v>6321453</v>
+        <v>6321455</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122872705</v>
+        <v>122872722</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583990</v>
+        <v>583996</v>
       </c>
       <c r="R18" t="n">
-        <v>6321458</v>
+        <v>6321453</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873636</v>
+        <v>122873533</v>
       </c>
       <c r="B20" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,34 +2703,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2739,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583840</v>
+        <v>584050</v>
       </c>
       <c r="R20" t="n">
-        <v>6321548</v>
+        <v>6321450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873525</v>
+        <v>122873552</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2814,43 +2822,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584055</v>
+        <v>583961</v>
       </c>
       <c r="R21" t="n">
-        <v>6321441</v>
+        <v>6321560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2902,7 +2902,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2921,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873603</v>
+        <v>122873525</v>
       </c>
       <c r="B22" t="n">
-        <v>91354</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,38 +2932,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583857</v>
+        <v>584055</v>
       </c>
       <c r="R22" t="n">
-        <v>6321560</v>
+        <v>6321441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3035,10 +3039,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122873563</v>
+        <v>122873636</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,35 +3051,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3083,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583933</v>
+        <v>583840</v>
       </c>
       <c r="R23" t="n">
-        <v>6321513</v>
+        <v>6321548</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,6 +3131,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3145,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873541</v>
+        <v>122873660</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3157,37 +3162,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3201,10 +3202,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583972</v>
+        <v>583872</v>
       </c>
       <c r="R24" t="n">
-        <v>6321426</v>
+        <v>6321489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,7 +3265,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873552</v>
+        <v>122873574</v>
       </c>
       <c r="B25" t="n">
         <v>57494</v>
@@ -3312,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583961</v>
+        <v>583893</v>
       </c>
       <c r="R25" t="n">
-        <v>6321560</v>
+        <v>6321535</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3374,7 +3375,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873574</v>
+        <v>122873563</v>
       </c>
       <c r="B26" t="n">
         <v>57494</v>
@@ -3422,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583893</v>
+        <v>583933</v>
       </c>
       <c r="R26" t="n">
-        <v>6321535</v>
+        <v>6321513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3484,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122873660</v>
+        <v>122873510</v>
       </c>
       <c r="B27" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,33 +3497,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3536,10 +3541,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583872</v>
+        <v>584086</v>
       </c>
       <c r="R27" t="n">
-        <v>6321489</v>
+        <v>6321399</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3599,10 +3604,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122873510</v>
+        <v>122873541</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3634,7 +3639,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3655,10 +3660,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584086</v>
+        <v>583972</v>
       </c>
       <c r="R28" t="n">
-        <v>6321399</v>
+        <v>6321426</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122873533</v>
+        <v>122873603</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>91362</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,43 +3735,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584050</v>
+        <v>583857</v>
       </c>
       <c r="R29" t="n">
-        <v>6321450</v>
+        <v>6321560</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -2244,7 +2244,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872713</v>
+        <v>122872697</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583965</v>
+        <v>583992</v>
       </c>
       <c r="R16" t="n">
-        <v>6321466</v>
+        <v>6321455</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872697</v>
+        <v>122872713</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583992</v>
+        <v>583965</v>
       </c>
       <c r="R17" t="n">
-        <v>6321455</v>
+        <v>6321466</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122843791</v>
+        <v>122852490</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584084</v>
+        <v>583911</v>
       </c>
       <c r="R2" t="n">
-        <v>6321402</v>
+        <v>6321488</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,39 +756,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845389</v>
+        <v>122844882</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,30 +808,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583986</v>
+        <v>583906</v>
       </c>
       <c r="R3" t="n">
-        <v>6321434</v>
+        <v>6321498</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,11 +876,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122844784</v>
+        <v>122852381</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,42 +914,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583938</v>
+        <v>584037</v>
       </c>
       <c r="R4" t="n">
-        <v>6321489</v>
+        <v>6321415</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,29 +983,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1119,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122844758</v>
+        <v>122852388</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1152,20 +1167,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583960</v>
+        <v>584009</v>
       </c>
       <c r="R6" t="n">
-        <v>6321445</v>
+        <v>6321450</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,39 +1215,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122844882</v>
+        <v>122843791</v>
       </c>
       <c r="B7" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,30 +1267,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1265,13 +1309,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583906</v>
+        <v>584084</v>
       </c>
       <c r="R7" t="n">
-        <v>6321498</v>
+        <v>6321402</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1359,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122852490</v>
+        <v>122845389</v>
       </c>
       <c r="B8" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,49 +1383,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583911</v>
+        <v>583986</v>
       </c>
       <c r="R8" t="n">
-        <v>6321488</v>
+        <v>6321434</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,19 +1448,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,26 +1464,25 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122852381</v>
+        <v>122844758</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1481,28 +1515,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584037</v>
+        <v>583960</v>
       </c>
       <c r="R9" t="n">
-        <v>6321415</v>
+        <v>6321445</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,50 +1555,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122852388</v>
+        <v>122844784</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,46 +1596,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584009</v>
+        <v>583938</v>
       </c>
       <c r="R10" t="n">
-        <v>6321450</v>
+        <v>6321489</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,50 +1661,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872764</v>
+        <v>122872737</v>
       </c>
       <c r="B11" t="n">
-        <v>95136</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,31 +1702,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1734,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583884</v>
+        <v>583966</v>
       </c>
       <c r="R11" t="n">
-        <v>6321510</v>
+        <v>6321457</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1786,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1908,7 +1915,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122872705</v>
+        <v>122872697</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1943,7 +1950,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1956,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583990</v>
+        <v>583992</v>
       </c>
       <c r="R13" t="n">
-        <v>6321458</v>
+        <v>6321455</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2019,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872699</v>
+        <v>122872705</v>
       </c>
       <c r="B14" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,30 +2038,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2067,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583992</v>
+        <v>583990</v>
       </c>
       <c r="R14" t="n">
-        <v>6321455</v>
+        <v>6321458</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2130,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872731</v>
+        <v>122872722</v>
       </c>
       <c r="B15" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,39 +2149,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2182,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583975</v>
+        <v>583996</v>
       </c>
       <c r="R15" t="n">
-        <v>6321433</v>
+        <v>6321453</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,6 +2229,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2244,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872697</v>
+        <v>122872699</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,30 +2260,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2466,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122872722</v>
+        <v>122872764</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,32 +2482,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583996</v>
+        <v>583884</v>
       </c>
       <c r="R18" t="n">
-        <v>6321453</v>
+        <v>6321510</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122872737</v>
+        <v>122872731</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2589,20 +2589,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583966</v>
+        <v>583975</v>
       </c>
       <c r="R19" t="n">
-        <v>6321457</v>
+        <v>6321433</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873533</v>
+        <v>122873563</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,43 +2703,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2747,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584050</v>
+        <v>583933</v>
       </c>
       <c r="R20" t="n">
-        <v>6321450</v>
+        <v>6321513</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2783,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2810,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873552</v>
+        <v>122873525</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2822,35 +2813,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2858,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583961</v>
+        <v>584055</v>
       </c>
       <c r="R21" t="n">
-        <v>6321560</v>
+        <v>6321441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2902,6 +2901,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873525</v>
+        <v>122873574</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,43 +2932,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2976,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584055</v>
+        <v>583893</v>
       </c>
       <c r="R22" t="n">
-        <v>6321441</v>
+        <v>6321535</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3020,7 +3012,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3039,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122873636</v>
+        <v>122873533</v>
       </c>
       <c r="B23" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3051,34 +3042,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3087,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583840</v>
+        <v>584050</v>
       </c>
       <c r="R23" t="n">
-        <v>6321548</v>
+        <v>6321450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873660</v>
+        <v>122873552</v>
       </c>
       <c r="B24" t="n">
-        <v>105471</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,39 +3161,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3202,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583872</v>
+        <v>583961</v>
       </c>
       <c r="R24" t="n">
-        <v>6321489</v>
+        <v>6321560</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3246,7 +3241,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3265,10 +3259,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873574</v>
+        <v>122873510</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,35 +3271,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3313,10 +3315,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583893</v>
+        <v>584086</v>
       </c>
       <c r="R25" t="n">
-        <v>6321535</v>
+        <v>6321399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3357,6 +3359,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3375,10 +3378,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873563</v>
+        <v>122873660</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,35 +3390,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3423,10 +3430,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583933</v>
+        <v>583872</v>
       </c>
       <c r="R26" t="n">
-        <v>6321513</v>
+        <v>6321489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3467,6 +3474,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3485,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122873510</v>
+        <v>122873636</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,42 +3505,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584086</v>
+        <v>583840</v>
       </c>
       <c r="R27" t="n">
-        <v>6321399</v>
+        <v>6321548</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852490</v>
+        <v>122844882</v>
       </c>
       <c r="B2" t="n">
         <v>105471</v>
@@ -710,26 +710,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583911</v>
+        <v>583906</v>
       </c>
       <c r="R2" t="n">
-        <v>6321488</v>
+        <v>6321498</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,50 +752,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122844882</v>
+        <v>122845389</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583906</v>
+        <v>583986</v>
       </c>
       <c r="R3" t="n">
-        <v>6321498</v>
+        <v>6321434</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,6 +861,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122852381</v>
+        <v>122844758</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -935,28 +925,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584037</v>
+        <v>583960</v>
       </c>
       <c r="R4" t="n">
-        <v>6321415</v>
+        <v>6321445</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,50 +965,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122843814</v>
+        <v>122843791</v>
       </c>
       <c r="B5" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,30 +1006,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1066,13 +1037,18 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584059</v>
+        <v>584084</v>
       </c>
       <c r="R5" t="n">
         <v>6321402</v>
@@ -1255,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122843791</v>
+        <v>122844784</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,40 +1243,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1309,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584084</v>
+        <v>583938</v>
       </c>
       <c r="R7" t="n">
-        <v>6321402</v>
+        <v>6321489</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,19 +1325,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122845389</v>
+        <v>122852381</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1406,22 +1372,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583986</v>
+        <v>584037</v>
       </c>
       <c r="R8" t="n">
-        <v>6321434</v>
+        <v>6321415</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,14 +1418,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,28 +1439,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122844758</v>
+        <v>122843814</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,41 +1470,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583960</v>
+        <v>584059</v>
       </c>
       <c r="R9" t="n">
-        <v>6321445</v>
+        <v>6321402</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,22 +1557,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122844784</v>
+        <v>122852490</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,42 +1581,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583938</v>
+        <v>583911</v>
       </c>
       <c r="R10" t="n">
-        <v>6321489</v>
+        <v>6321488</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,39 +1650,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872737</v>
+        <v>122872764</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,39 +1702,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1742,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583966</v>
+        <v>583884</v>
       </c>
       <c r="R11" t="n">
-        <v>6321457</v>
+        <v>6321510</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,6 +1778,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2137,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872722</v>
+        <v>122872699</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,30 +2142,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2185,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583996</v>
+        <v>583992</v>
       </c>
       <c r="R15" t="n">
-        <v>6321453</v>
+        <v>6321455</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2248,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872699</v>
+        <v>122872713</v>
       </c>
       <c r="B16" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,30 +2253,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2296,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583992</v>
+        <v>583965</v>
       </c>
       <c r="R16" t="n">
-        <v>6321455</v>
+        <v>6321466</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872713</v>
+        <v>122872722</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2394,7 +2387,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2407,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583965</v>
+        <v>583996</v>
       </c>
       <c r="R17" t="n">
-        <v>6321466</v>
+        <v>6321453</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122872764</v>
+        <v>122872731</v>
       </c>
       <c r="B18" t="n">
-        <v>95136</v>
+        <v>57848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,27 +2479,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2514,10 +2515,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583884</v>
+        <v>583975</v>
       </c>
       <c r="R18" t="n">
-        <v>6321510</v>
+        <v>6321433</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2558,7 +2559,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122872731</v>
+        <v>122872737</v>
       </c>
       <c r="B19" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2589,20 +2589,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583975</v>
+        <v>583966</v>
       </c>
       <c r="R19" t="n">
-        <v>6321433</v>
+        <v>6321457</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873563</v>
+        <v>122873552</v>
       </c>
       <c r="B20" t="n">
         <v>57494</v>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583933</v>
+        <v>583961</v>
       </c>
       <c r="R20" t="n">
-        <v>6321513</v>
+        <v>6321560</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,7 +2801,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873525</v>
+        <v>122873533</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584055</v>
+        <v>584050</v>
       </c>
       <c r="R21" t="n">
-        <v>6321441</v>
+        <v>6321450</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873574</v>
+        <v>122873563</v>
       </c>
       <c r="B22" t="n">
         <v>57494</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583893</v>
+        <v>583933</v>
       </c>
       <c r="R22" t="n">
-        <v>6321535</v>
+        <v>6321513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122873533</v>
+        <v>122873660</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,37 +3042,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3086,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584050</v>
+        <v>583872</v>
       </c>
       <c r="R23" t="n">
-        <v>6321450</v>
+        <v>6321489</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873552</v>
+        <v>122873603</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>91362</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,35 +3157,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3197,7 +3196,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583961</v>
+        <v>583857</v>
       </c>
       <c r="R24" t="n">
         <v>6321560</v>
@@ -3241,6 +3240,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873510</v>
+        <v>122873574</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3271,43 +3271,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3315,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584086</v>
+        <v>583893</v>
       </c>
       <c r="R25" t="n">
-        <v>6321399</v>
+        <v>6321535</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3359,7 +3351,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3378,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873660</v>
+        <v>122873541</v>
       </c>
       <c r="B26" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,33 +3381,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3430,10 +3425,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583872</v>
+        <v>583972</v>
       </c>
       <c r="R26" t="n">
-        <v>6321489</v>
+        <v>6321426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3599,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122873541</v>
+        <v>122873525</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -3639,7 +3634,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3660,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583972</v>
+        <v>584055</v>
       </c>
       <c r="R28" t="n">
-        <v>6321426</v>
+        <v>6321441</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3723,10 +3718,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122873603</v>
+        <v>122873510</v>
       </c>
       <c r="B29" t="n">
-        <v>91362</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3735,38 +3730,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583857</v>
+        <v>584086</v>
       </c>
       <c r="R29" t="n">
-        <v>6321560</v>
+        <v>6321399</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845389</v>
+        <v>122852490</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,45 +793,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583986</v>
+        <v>583911</v>
       </c>
       <c r="R3" t="n">
-        <v>6321434</v>
+        <v>6321488</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,14 +862,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,25 +883,26 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122844758</v>
+        <v>122852388</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -925,20 +935,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583960</v>
+        <v>584009</v>
       </c>
       <c r="R4" t="n">
-        <v>6321445</v>
+        <v>6321450</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,36 +983,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122843791</v>
+        <v>122852381</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1029,32 +1058,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584084</v>
+        <v>584037</v>
       </c>
       <c r="R5" t="n">
-        <v>6321402</v>
+        <v>6321415</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,36 +1104,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122852388</v>
+        <v>122845389</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1145,26 +1179,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584009</v>
+        <v>583986</v>
       </c>
       <c r="R6" t="n">
-        <v>6321450</v>
+        <v>6321434</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,19 +1221,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,19 +1237,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1337,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122852381</v>
+        <v>122843814</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,49 +1373,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584037</v>
+        <v>584059</v>
       </c>
       <c r="R8" t="n">
-        <v>6321415</v>
+        <v>6321402</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,50 +1443,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122843814</v>
+        <v>122843791</v>
       </c>
       <c r="B9" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,30 +1484,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1501,13 +1515,18 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584059</v>
+        <v>584084</v>
       </c>
       <c r="R9" t="n">
         <v>6321402</v>
@@ -1569,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122852490</v>
+        <v>122844758</v>
       </c>
       <c r="B10" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,49 +1600,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583911</v>
+        <v>583960</v>
       </c>
       <c r="R10" t="n">
-        <v>6321488</v>
+        <v>6321445</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,40 +1661,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122872727</v>
+        <v>122872722</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583975</v>
+        <v>583996</v>
       </c>
       <c r="R12" t="n">
-        <v>6321433</v>
+        <v>6321453</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122872697</v>
+        <v>122872727</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583992</v>
+        <v>583975</v>
       </c>
       <c r="R13" t="n">
-        <v>6321455</v>
+        <v>6321433</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872705</v>
+        <v>122872737</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,35 +2031,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2067,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583990</v>
+        <v>583966</v>
       </c>
       <c r="R14" t="n">
-        <v>6321458</v>
+        <v>6321457</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2111,7 +2115,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872699</v>
+        <v>122872705</v>
       </c>
       <c r="B15" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,30 +2145,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2178,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583992</v>
+        <v>583990</v>
       </c>
       <c r="R15" t="n">
-        <v>6321455</v>
+        <v>6321458</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2352,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872722</v>
+        <v>122872697</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2387,7 +2390,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2400,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583996</v>
+        <v>583992</v>
       </c>
       <c r="R17" t="n">
-        <v>6321453</v>
+        <v>6321455</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2577,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122872737</v>
+        <v>122872699</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2589,39 +2592,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2629,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583966</v>
+        <v>583992</v>
       </c>
       <c r="R19" t="n">
-        <v>6321457</v>
+        <v>6321455</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2673,6 +2672,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873552</v>
+        <v>122873563</v>
       </c>
       <c r="B20" t="n">
         <v>57494</v>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583961</v>
+        <v>583933</v>
       </c>
       <c r="R20" t="n">
-        <v>6321560</v>
+        <v>6321513</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873533</v>
+        <v>122873660</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,37 +2813,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2857,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584050</v>
+        <v>583872</v>
       </c>
       <c r="R21" t="n">
-        <v>6321450</v>
+        <v>6321489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2920,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873563</v>
+        <v>122873510</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,35 +2928,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2968,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583933</v>
+        <v>584086</v>
       </c>
       <c r="R22" t="n">
-        <v>6321513</v>
+        <v>6321399</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,6 +3016,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3030,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122873660</v>
+        <v>122873541</v>
       </c>
       <c r="B23" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,33 +3047,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3082,10 +3091,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583872</v>
+        <v>583972</v>
       </c>
       <c r="R23" t="n">
-        <v>6321489</v>
+        <v>6321426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3145,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873603</v>
+        <v>122873533</v>
       </c>
       <c r="B24" t="n">
-        <v>91362</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3157,38 +3166,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3196,10 +3210,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583857</v>
+        <v>584050</v>
       </c>
       <c r="R24" t="n">
-        <v>6321560</v>
+        <v>6321450</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3259,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873574</v>
+        <v>122873603</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>91362</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3271,35 +3285,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3307,10 +3324,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583893</v>
+        <v>583857</v>
       </c>
       <c r="R25" t="n">
-        <v>6321535</v>
+        <v>6321560</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3351,6 +3368,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3369,7 +3387,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873541</v>
+        <v>122873525</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3404,7 +3422,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3425,10 +3443,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583972</v>
+        <v>584055</v>
       </c>
       <c r="R26" t="n">
-        <v>6321426</v>
+        <v>6321441</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3488,10 +3506,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122873636</v>
+        <v>122873552</v>
       </c>
       <c r="B27" t="n">
-        <v>95136</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,35 +3518,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3536,10 +3554,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583840</v>
+        <v>583961</v>
       </c>
       <c r="R27" t="n">
-        <v>6321548</v>
+        <v>6321560</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3580,7 +3598,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3599,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122873525</v>
+        <v>122873574</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3611,43 +3628,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3655,10 +3664,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584055</v>
+        <v>583893</v>
       </c>
       <c r="R28" t="n">
-        <v>6321441</v>
+        <v>6321535</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3699,7 +3708,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3718,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122873510</v>
+        <v>122873636</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,42 +3738,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584086</v>
+        <v>583840</v>
       </c>
       <c r="R29" t="n">
-        <v>6321399</v>
+        <v>6321548</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122844882</v>
+        <v>122852490</v>
       </c>
       <c r="B2" t="n">
         <v>105471</v>
@@ -710,22 +710,26 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583906</v>
+        <v>583911</v>
       </c>
       <c r="R2" t="n">
-        <v>6321498</v>
+        <v>6321488</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,36 +756,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852490</v>
+        <v>122844882</v>
       </c>
       <c r="B3" t="n">
         <v>105471</v>
@@ -816,26 +831,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583911</v>
+        <v>583906</v>
       </c>
       <c r="R3" t="n">
-        <v>6321488</v>
+        <v>6321498</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,40 +873,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852490</v>
+        <v>122844882</v>
       </c>
       <c r="B2" t="n">
         <v>105471</v>
@@ -710,26 +710,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583911</v>
+        <v>583906</v>
       </c>
       <c r="R2" t="n">
-        <v>6321488</v>
+        <v>6321498</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,47 +752,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122844882</v>
+        <v>122852490</v>
       </c>
       <c r="B3" t="n">
         <v>105471</v>
@@ -831,22 +816,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583906</v>
+        <v>583911</v>
       </c>
       <c r="R3" t="n">
-        <v>6321498</v>
+        <v>6321488</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,29 +862,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852490</v>
+        <v>122844882</v>
       </c>
       <c r="B2" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,26 +710,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583911</v>
+        <v>583906</v>
       </c>
       <c r="R2" t="n">
-        <v>6321488</v>
+        <v>6321498</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,50 +752,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122844882</v>
+        <v>122852490</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,22 +816,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583906</v>
+        <v>583911</v>
       </c>
       <c r="R3" t="n">
-        <v>6321498</v>
+        <v>6321488</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,39 +862,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122852388</v>
+        <v>122844758</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,28 +935,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584009</v>
+        <v>583960</v>
       </c>
       <c r="R4" t="n">
-        <v>6321450</v>
+        <v>6321445</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,50 +975,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122852381</v>
+        <v>122852388</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,7 +1039,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1071,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584037</v>
+        <v>584009</v>
       </c>
       <c r="R5" t="n">
-        <v>6321415</v>
+        <v>6321450</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1144,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122845389</v>
+        <v>122852381</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,22 +1160,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583986</v>
+        <v>584037</v>
       </c>
       <c r="R6" t="n">
-        <v>6321434</v>
+        <v>6321415</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,14 +1206,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,28 +1227,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122844784</v>
+        <v>122845389</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,30 +1258,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583938</v>
+        <v>583986</v>
       </c>
       <c r="R7" t="n">
-        <v>6321489</v>
+        <v>6321434</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,6 +1326,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122843814</v>
+        <v>122843791</v>
       </c>
       <c r="B8" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,30 +1369,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1404,13 +1400,18 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584059</v>
+        <v>584084</v>
       </c>
       <c r="R8" t="n">
         <v>6321402</v>
@@ -1472,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122843791</v>
+        <v>122844784</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,40 +1485,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584084</v>
+        <v>583938</v>
       </c>
       <c r="R9" t="n">
-        <v>6321402</v>
+        <v>6321489</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,22 +1567,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122844758</v>
+        <v>122843814</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,41 +1591,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583960</v>
+        <v>584059</v>
       </c>
       <c r="R10" t="n">
-        <v>6321445</v>
+        <v>6321402</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,22 +1678,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872764</v>
+        <v>122872699</v>
       </c>
       <c r="B11" t="n">
-        <v>95136</v>
+        <v>105474</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,24 +1706,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1734,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583884</v>
+        <v>583992</v>
       </c>
       <c r="R11" t="n">
-        <v>6321510</v>
+        <v>6321455</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,7 +1804,7 @@
         <v>122872722</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,7 +1915,7 @@
         <v>122872727</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872737</v>
+        <v>122872713</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,39 +2035,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583966</v>
+        <v>583965</v>
       </c>
       <c r="R14" t="n">
-        <v>6321457</v>
+        <v>6321466</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2115,6 +2115,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2133,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872705</v>
+        <v>122872697</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,7 +2169,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2181,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583990</v>
+        <v>583992</v>
       </c>
       <c r="R15" t="n">
-        <v>6321458</v>
+        <v>6321455</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872713</v>
+        <v>122872705</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,7 +2280,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2292,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583965</v>
+        <v>583990</v>
       </c>
       <c r="R16" t="n">
-        <v>6321466</v>
+        <v>6321458</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2355,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872697</v>
+        <v>122872731</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,35 +2368,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2403,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583992</v>
+        <v>583975</v>
       </c>
       <c r="R17" t="n">
-        <v>6321455</v>
+        <v>6321433</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2447,7 +2452,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2466,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122872731</v>
+        <v>122872764</v>
       </c>
       <c r="B18" t="n">
-        <v>57848</v>
+        <v>95139</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2482,35 +2486,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2518,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583975</v>
+        <v>583884</v>
       </c>
       <c r="R18" t="n">
-        <v>6321433</v>
+        <v>6321510</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,6 +2558,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2580,10 +2577,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122872699</v>
+        <v>122872737</v>
       </c>
       <c r="B19" t="n">
-        <v>105471</v>
+        <v>57497</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,35 +2589,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2628,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583992</v>
+        <v>583966</v>
       </c>
       <c r="R19" t="n">
-        <v>6321455</v>
+        <v>6321457</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2672,7 +2673,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873563</v>
+        <v>122873603</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>91365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,35 +2703,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2739,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583933</v>
+        <v>583857</v>
       </c>
       <c r="R20" t="n">
-        <v>6321513</v>
+        <v>6321560</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,6 +2786,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2801,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873660</v>
+        <v>122873563</v>
       </c>
       <c r="B21" t="n">
-        <v>105471</v>
+        <v>57497</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,39 +2817,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583872</v>
+        <v>583933</v>
       </c>
       <c r="R21" t="n">
-        <v>6321489</v>
+        <v>6321513</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2897,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2916,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873510</v>
+        <v>122873574</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2928,43 +2927,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2972,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584086</v>
+        <v>583893</v>
       </c>
       <c r="R22" t="n">
-        <v>6321399</v>
+        <v>6321535</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,7 +3007,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3035,10 +3025,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122873541</v>
+        <v>122873510</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3070,7 +3060,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3091,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583972</v>
+        <v>584086</v>
       </c>
       <c r="R23" t="n">
-        <v>6321426</v>
+        <v>6321399</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3154,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873533</v>
+        <v>122873636</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3166,42 +3156,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3210,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584050</v>
+        <v>583840</v>
       </c>
       <c r="R24" t="n">
-        <v>6321450</v>
+        <v>6321548</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,10 +3255,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873603</v>
+        <v>122873533</v>
       </c>
       <c r="B25" t="n">
-        <v>91362</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,38 +3267,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3324,10 +3311,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583857</v>
+        <v>584050</v>
       </c>
       <c r="R25" t="n">
-        <v>6321560</v>
+        <v>6321450</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3387,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873525</v>
+        <v>122873660</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3399,37 +3386,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3443,10 +3426,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584055</v>
+        <v>583872</v>
       </c>
       <c r="R26" t="n">
-        <v>6321441</v>
+        <v>6321489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3506,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122873552</v>
+        <v>122873541</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3518,35 +3501,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3554,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583961</v>
+        <v>583972</v>
       </c>
       <c r="R27" t="n">
-        <v>6321560</v>
+        <v>6321426</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3598,6 +3589,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3616,10 +3608,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122873574</v>
+        <v>122873552</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,10 +3656,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583893</v>
+        <v>583961</v>
       </c>
       <c r="R28" t="n">
-        <v>6321535</v>
+        <v>6321560</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3726,10 +3718,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122873636</v>
+        <v>122873525</v>
       </c>
       <c r="B29" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3738,34 +3730,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583840</v>
+        <v>584055</v>
       </c>
       <c r="R29" t="n">
-        <v>6321548</v>
+        <v>6321441</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122844882</v>
+        <v>122843814</v>
       </c>
       <c r="B2" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583906</v>
+        <v>584059</v>
       </c>
       <c r="R2" t="n">
-        <v>6321498</v>
+        <v>6321402</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852490</v>
+        <v>122852388</v>
       </c>
       <c r="B3" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -829,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583911</v>
+        <v>584009</v>
       </c>
       <c r="R3" t="n">
-        <v>6321488</v>
+        <v>6321450</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122844758</v>
+        <v>122845389</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +940,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583960</v>
+        <v>583986</v>
       </c>
       <c r="R4" t="n">
-        <v>6321445</v>
+        <v>6321434</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,6 +987,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122852388</v>
+        <v>122843791</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,26 +1053,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584009</v>
+        <v>584084</v>
       </c>
       <c r="R5" t="n">
-        <v>6321450</v>
+        <v>6321402</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,50 +1105,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122852381</v>
+        <v>122852490</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,30 +1146,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1173,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584037</v>
+        <v>583911</v>
       </c>
       <c r="R6" t="n">
-        <v>6321415</v>
+        <v>6321488</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1246,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122845389</v>
+        <v>122852381</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,22 +1290,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583986</v>
+        <v>584037</v>
       </c>
       <c r="R7" t="n">
-        <v>6321434</v>
+        <v>6321415</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,14 +1336,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,28 +1357,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122843791</v>
+        <v>122844882</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,40 +1388,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584084</v>
+        <v>583906</v>
       </c>
       <c r="R8" t="n">
-        <v>6321402</v>
+        <v>6321498</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122844784</v>
+        <v>122844758</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,45 +1494,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583938</v>
+        <v>583960</v>
       </c>
       <c r="R9" t="n">
-        <v>6321489</v>
+        <v>6321445</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122843814</v>
+        <v>122844784</v>
       </c>
       <c r="B10" t="n">
-        <v>105474</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,35 +1596,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1628,13 +1628,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584059</v>
+        <v>583938</v>
       </c>
       <c r="R10" t="n">
-        <v>6321402</v>
+        <v>6321489</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,22 +1678,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872699</v>
+        <v>122872713</v>
       </c>
       <c r="B11" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,30 +1702,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583992</v>
+        <v>583965</v>
       </c>
       <c r="R11" t="n">
-        <v>6321455</v>
+        <v>6321466</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1804,7 +1804,7 @@
         <v>122872722</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122872727</v>
+        <v>122872764</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,32 +1924,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1960,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583975</v>
+        <v>583884</v>
       </c>
       <c r="R13" t="n">
-        <v>6321433</v>
+        <v>6321510</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2023,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872713</v>
+        <v>122872737</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,35 +2031,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583965</v>
+        <v>583966</v>
       </c>
       <c r="R14" t="n">
-        <v>6321466</v>
+        <v>6321457</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2115,7 +2115,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>122872697</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2245,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872705</v>
+        <v>122872727</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,7 +2279,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2293,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583990</v>
+        <v>583975</v>
       </c>
       <c r="R16" t="n">
-        <v>6321458</v>
+        <v>6321433</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2356,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872731</v>
+        <v>122872705</v>
       </c>
       <c r="B17" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2394,13 +2393,9 @@
           <t>5</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2408,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583975</v>
+        <v>583990</v>
       </c>
       <c r="R17" t="n">
-        <v>6321433</v>
+        <v>6321458</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2452,6 +2447,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122872764</v>
+        <v>122872731</v>
       </c>
       <c r="B18" t="n">
-        <v>95139</v>
+        <v>57851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,27 +2482,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2514,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583884</v>
+        <v>583975</v>
       </c>
       <c r="R18" t="n">
-        <v>6321510</v>
+        <v>6321433</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2558,7 +2562,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2577,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122872737</v>
+        <v>122872699</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>105476</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2589,39 +2592,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2629,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583966</v>
+        <v>583992</v>
       </c>
       <c r="R19" t="n">
-        <v>6321457</v>
+        <v>6321455</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2673,6 +2672,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873603</v>
+        <v>122873541</v>
       </c>
       <c r="B20" t="n">
-        <v>91365</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,38 +2703,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2742,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583857</v>
+        <v>583972</v>
       </c>
       <c r="R20" t="n">
-        <v>6321560</v>
+        <v>6321426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,7 +2810,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873563</v>
+        <v>122873574</v>
       </c>
       <c r="B21" t="n">
         <v>57497</v>
@@ -2853,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583933</v>
+        <v>583893</v>
       </c>
       <c r="R21" t="n">
-        <v>6321513</v>
+        <v>6321535</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,7 +2920,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873574</v>
+        <v>122873563</v>
       </c>
       <c r="B22" t="n">
         <v>57497</v>
@@ -2963,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583893</v>
+        <v>583933</v>
       </c>
       <c r="R22" t="n">
-        <v>6321535</v>
+        <v>6321513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3025,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122873510</v>
+        <v>122873552</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,43 +3042,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3081,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584086</v>
+        <v>583961</v>
       </c>
       <c r="R23" t="n">
-        <v>6321399</v>
+        <v>6321560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,7 +3122,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3144,10 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873636</v>
+        <v>122873603</v>
       </c>
       <c r="B24" t="n">
-        <v>95139</v>
+        <v>91367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,31 +3156,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3192,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583840</v>
+        <v>583857</v>
       </c>
       <c r="R24" t="n">
-        <v>6321548</v>
+        <v>6321560</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873533</v>
+        <v>122873660</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,37 +3266,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3311,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584050</v>
+        <v>583872</v>
       </c>
       <c r="R25" t="n">
-        <v>6321450</v>
+        <v>6321489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3374,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873660</v>
+        <v>122873510</v>
       </c>
       <c r="B26" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,33 +3381,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3426,10 +3425,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583872</v>
+        <v>584086</v>
       </c>
       <c r="R26" t="n">
-        <v>6321489</v>
+        <v>6321399</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3489,10 +3488,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122873541</v>
+        <v>122873636</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,42 +3500,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3545,10 +3536,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583972</v>
+        <v>583840</v>
       </c>
       <c r="R27" t="n">
-        <v>6321426</v>
+        <v>6321548</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3608,10 +3599,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122873552</v>
+        <v>122873533</v>
       </c>
       <c r="B28" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3620,35 +3611,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3656,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583961</v>
+        <v>584050</v>
       </c>
       <c r="R28" t="n">
-        <v>6321560</v>
+        <v>6321450</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3700,6 +3699,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>122873525</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 2569-2025 artfynd.xlsx
+++ b/artfynd/A 2569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122843814</v>
+        <v>122845389</v>
       </c>
       <c r="B2" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584059</v>
+        <v>583986</v>
       </c>
       <c r="R2" t="n">
-        <v>6321402</v>
+        <v>6321434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +757,11 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>70-tal plantor utspridda</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852388</v>
+        <v>122844784</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +798,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584009</v>
+        <v>583938</v>
       </c>
       <c r="R3" t="n">
-        <v>6321450</v>
+        <v>6321489</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,50 +863,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122845389</v>
+        <v>122844882</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,30 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583986</v>
+        <v>583906</v>
       </c>
       <c r="R4" t="n">
-        <v>6321434</v>
+        <v>6321498</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>70-tal plantor utspridda</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122843791</v>
+        <v>122843814</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,30 +1010,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1061,18 +1041,13 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584084</v>
+        <v>584059</v>
       </c>
       <c r="R5" t="n">
         <v>6321402</v>
@@ -1134,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122852490</v>
+        <v>122844758</v>
       </c>
       <c r="B6" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,49 +1121,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583911</v>
+        <v>583960</v>
       </c>
       <c r="R6" t="n">
-        <v>6321488</v>
+        <v>6321445</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,50 +1182,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122852381</v>
+        <v>122843791</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,26 +1246,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vidflagen, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584037</v>
+        <v>584084</v>
       </c>
       <c r="R7" t="n">
-        <v>6321415</v>
+        <v>6321402</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,50 +1298,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122844882</v>
+        <v>122852388</v>
       </c>
       <c r="B8" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,45 +1339,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583906</v>
+        <v>584009</v>
       </c>
       <c r="R8" t="n">
-        <v>6321498</v>
+        <v>6321450</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,39 +1408,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122844758</v>
+        <v>122852490</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,41 +1460,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583960</v>
+        <v>583911</v>
       </c>
       <c r="R9" t="n">
-        <v>6321445</v>
+        <v>6321488</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1555,39 +1529,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122844784</v>
+        <v>122852381</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,42 +1581,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Vidflagen, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583938</v>
+        <v>584037</v>
       </c>
       <c r="R10" t="n">
-        <v>6321489</v>
+        <v>6321415</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,39 +1650,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122872713</v>
+        <v>122872737</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,35 +1702,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1738,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583965</v>
+        <v>583966</v>
       </c>
       <c r="R11" t="n">
-        <v>6321466</v>
+        <v>6321457</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1786,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1801,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122872722</v>
+        <v>122872731</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,35 +1816,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1849,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583996</v>
+        <v>583975</v>
       </c>
       <c r="R12" t="n">
-        <v>6321453</v>
+        <v>6321433</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1893,7 +1900,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1912,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122872764</v>
+        <v>122872705</v>
       </c>
       <c r="B13" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,28 +1930,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1956,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583884</v>
+        <v>583990</v>
       </c>
       <c r="R13" t="n">
-        <v>6321510</v>
+        <v>6321458</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2019,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122872737</v>
+        <v>122872764</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>95147</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,39 +2041,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2071,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583966</v>
+        <v>583884</v>
       </c>
       <c r="R14" t="n">
-        <v>6321457</v>
+        <v>6321510</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2115,6 +2117,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2133,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122872697</v>
+        <v>122872722</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,7 +2171,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2181,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583992</v>
+        <v>583996</v>
       </c>
       <c r="R15" t="n">
-        <v>6321455</v>
+        <v>6321453</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122872727</v>
+        <v>122872713</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,7 +2282,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2292,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583975</v>
+        <v>583965</v>
       </c>
       <c r="R16" t="n">
-        <v>6321433</v>
+        <v>6321466</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2355,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122872705</v>
+        <v>122872727</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,7 +2393,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2403,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583990</v>
+        <v>583975</v>
       </c>
       <c r="R17" t="n">
-        <v>6321458</v>
+        <v>6321433</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2466,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122872731</v>
+        <v>122872697</v>
       </c>
       <c r="B18" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,39 +2481,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2518,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583975</v>
+        <v>583992</v>
       </c>
       <c r="R18" t="n">
-        <v>6321433</v>
+        <v>6321455</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,6 +2561,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>122872699</v>
       </c>
       <c r="B19" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122873541</v>
+        <v>122873574</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,43 +2703,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2747,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583972</v>
+        <v>583893</v>
       </c>
       <c r="R20" t="n">
-        <v>6321426</v>
+        <v>6321535</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2783,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2810,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122873574</v>
+        <v>122873510</v>
       </c>
       <c r="B21" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2822,35 +2813,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2858,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583893</v>
+        <v>584086</v>
       </c>
       <c r="R21" t="n">
-        <v>6321535</v>
+        <v>6321399</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2902,6 +2901,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122873563</v>
+        <v>122873525</v>
       </c>
       <c r="B22" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,35 +2932,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2968,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583933</v>
+        <v>584055</v>
       </c>
       <c r="R22" t="n">
-        <v>6321513</v>
+        <v>6321441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,6 +3020,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3030,10 +3039,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122873552</v>
+        <v>122873541</v>
       </c>
       <c r="B23" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,35 +3051,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3078,10 +3095,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583961</v>
+        <v>583972</v>
       </c>
       <c r="R23" t="n">
-        <v>6321560</v>
+        <v>6321426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,6 +3139,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3140,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122873603</v>
+        <v>122873636</v>
       </c>
       <c r="B24" t="n">
-        <v>91367</v>
+        <v>95147</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,34 +3174,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3191,10 +3206,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583857</v>
+        <v>583840</v>
       </c>
       <c r="R24" t="n">
-        <v>6321560</v>
+        <v>6321548</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122873660</v>
+        <v>122873603</v>
       </c>
       <c r="B25" t="n">
-        <v>105476</v>
+        <v>91373</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3270,35 +3285,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3306,10 +3320,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583872</v>
+        <v>583857</v>
       </c>
       <c r="R25" t="n">
-        <v>6321489</v>
+        <v>6321560</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122873510</v>
+        <v>122873552</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3381,43 +3395,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3425,10 +3431,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584086</v>
+        <v>583961</v>
       </c>
       <c r="R26" t="n">
-        <v>6321399</v>
+        <v>6321560</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3469,7 +3475,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3488,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122873636</v>
+        <v>122873660</v>
       </c>
       <c r="B27" t="n">
-        <v>95141</v>
+        <v>105482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3504,30 +3509,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3536,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583840</v>
+        <v>583872</v>
       </c>
       <c r="R27" t="n">
-        <v>6321548</v>
+        <v>6321489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3602,7 +3611,7 @@
         <v>122873533</v>
       </c>
       <c r="B28" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3718,10 +3727,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122873525</v>
+        <v>122873563</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,43 +3739,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3774,10 +3775,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584055</v>
+        <v>583933</v>
       </c>
       <c r="R29" t="n">
-        <v>6321441</v>
+        <v>6321513</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,7 +3819,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
